--- a/output/2025_A04_SECCION_L_TABLAS.xlsx
+++ b/output/2025_A04_SECCION_L_TABLAS.xlsx
@@ -75,7 +75,7 @@
     <t>Servicio de Salud Metropolitano Sur</t>
   </si>
   <si>
-    <t>Servicio de Salud Metropolitano Sur Oriente</t>
+    <t>Servicio de Salud Metropolitano Sur - Oriente</t>
   </si>
   <si>
     <t>nombre_comuna</t>
@@ -282,10 +282,10 @@
     <t>Posta de Salud Rural Santa Marta de Liray</t>
   </si>
   <si>
-    <t>Centro Comunitario de Salud Familiar Alberto Bachelet</t>
+    <t>CECOSF Haydeé Sepúlveda</t>
   </si>
   <si>
-    <t>Centro Comunitario de Salud Familiar Dr. José Symón Ojeda</t>
+    <t>Centro Comunitario de Salud Familiar Alberto Bachelet</t>
   </si>
   <si>
     <t>Centro Comunitario de Salud Familiar Dr. Lucas Sierra</t>
@@ -888,7 +888,7 @@
     <t>Centro de Salud Familiar Huertos Familiares</t>
   </si>
   <si>
-    <t>Hospital de Til Til</t>
+    <t>Hospital Comunitario de Til Til</t>
   </si>
   <si>
     <t>Posta de Salud Rural La Capilla de Caleu</t>
@@ -7318,13 +7318,13 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7335,13 +7335,13 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -11510,7 +11510,7 @@
         <v>81</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -11519,7 +11519,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -11527,7 +11527,7 @@
         <v>82</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -11536,7 +11536,7 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -15714,7 +15714,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -15731,7 +15731,7 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -20051,7 +20051,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -20068,7 +20068,7 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:6">
